--- a/outputs/monitor_xlsx/20260305.xlsx
+++ b/outputs/monitor_xlsx/20260305.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2398,7 +2398,7 @@
         <v>-106279</v>
       </c>
       <c r="N24" t="n">
-        <v>22.44</v>
+        <v>16.11</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2456,6 +2456,59 @@
       <c r="O25" t="inlineStr">
         <is>
           <t>偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="E26" t="n">
+        <v>297</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-172</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-28</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>327</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1589</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-8890</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>主力積極賣出</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260305.xlsx
+++ b/outputs/monitor_xlsx/20260305.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -526,215 +526,236 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>美債10年殖利率</t>
+          <t>加權指數 (TWII)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.15%</t>
+          <t>33672.94</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+1.72%</t>
-        </is>
-      </c>
+          <t>+2.57%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>黃金指數 (GC=F)</t>
+          <t>櫃買指數 (OTC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5092.4$</t>
+          <t>304.21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.54%</t>
-        </is>
-      </c>
+          <t>+3.54%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>貨幣</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>美元/台幣匯率</t>
+          <t>台指近月期貨</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.63</t>
+          <t>33639.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33%</t>
-        </is>
-      </c>
+          <t>+2.34%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>現貨</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>費半指數 (SOX)</t>
+          <t>美債10年殖利率</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7821.76</t>
+          <t>4.15%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-1.17%</t>
-        </is>
-      </c>
+          <t>+1.72%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>情緒</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>恐慌指數 (VIX)</t>
+          <t>黃金指數 (GC=F)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>5065.3$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+12.29%</t>
-        </is>
-      </c>
+          <t>-1.07%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>貨幣</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>外資現貨</t>
+          <t>美元/台幣匯率</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-514.95億</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>-584.74億</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-2923.71億</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-68.44億</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-1368.87億</t>
-        </is>
-      </c>
+          <t>31.63</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-0.33%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>現貨</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>投信現貨</t>
+          <t>費半指數 (SOX)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>144.67億</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>64.83億</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>324.17億</t>
-        </is>
-      </c>
+          <t>7821.76</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-1.17%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>情緒</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>選擇權 P/C Ratio</t>
+          <t>恐慌指數 (VIX)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>128.98%</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>134.73%</t>
-        </is>
-      </c>
+          <t>23.75</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>+12.29%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>原物料</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>三大法人合計</t>
+          <t>WTI原油期貨</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-458.02億</t>
-        </is>
-      </c>
+          <t>81.01$</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>+8.51%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -744,54 +765,175 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>外資期貨未平倉</t>
+          <t>外資現貨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11679口</t>
-        </is>
-      </c>
+          <t>-514.95億</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16801口</t>
+          <t>-584.74億</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-2923.71億</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-68.44億</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-1368.87億</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>投信現貨</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>144.67億</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>64.83億</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>324.17億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>選擇權 P/C Ratio</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>None%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>三大法人合計</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-458.02億</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>外資期貨未平倉</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>11679口</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>16801口</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>結算</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>融資融券變化</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>-31.18億</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>2.79億</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>13.96億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-4.51億</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-90.13億</t>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-3.19億</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-63.77億</t>
         </is>
       </c>
     </row>
@@ -878,6 +1020,10 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -941,7 +1087,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-4.51億</t>
+          <t>-3.19億</t>
         </is>
       </c>
     </row>
@@ -953,7 +1099,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-90.13億</t>
+          <t>-63.77億</t>
         </is>
       </c>
     </row>
@@ -972,7 +1118,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>134.73%</t>
+          <t>None%</t>
         </is>
       </c>
     </row>
@@ -999,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1017,14 +1163,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1034,7 +1179,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1113,40 +1257,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1181,13 +1320,13 @@
         <v>-76899</v>
       </c>
       <c r="H4" t="n">
-        <v>-428767</v>
+        <v>-290402</v>
       </c>
       <c r="I4" t="n">
         <v>2300</v>
       </c>
       <c r="J4" t="n">
-        <v>13486</v>
+        <v>5272</v>
       </c>
       <c r="K4" t="n">
         <v>48938</v>
@@ -1196,20 +1335,12 @@
         <v>11144</v>
       </c>
       <c r="M4" t="n">
-        <v>45195</v>
+        <v>36862</v>
       </c>
       <c r="N4" t="n">
         <v>-4279950</v>
       </c>
-      <c r="O4" t="n">
-        <v>-2.51</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1218,41 +1349,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00708L</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S&amp;P黃金正2</t>
-        </is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>951</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3097</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-54</v>
+        <v>-292</v>
       </c>
       <c r="H5" t="n">
-        <v>-671</v>
+        <v>1457</v>
+      </c>
+      <c r="I5" t="n">
+        <v>92</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-259</v>
       </c>
       <c r="K5" t="n">
-        <v>1089</v>
+        <v>139</v>
       </c>
       <c r="L5" t="n">
-        <v>10136</v>
+        <v>2777</v>
       </c>
       <c r="M5" t="n">
-        <v>49012</v>
+        <v>11390</v>
       </c>
       <c r="N5" t="n">
-        <v>-27548</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+        <v>-78802</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1261,12 +1404,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1275,47 +1418,39 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>951</v>
+        <v>1335</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>4.74</v>
+        <v>6.37</v>
       </c>
       <c r="F6" t="n">
-        <v>3097</v>
+        <v>13686</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-292</v>
+        <v>-1505</v>
       </c>
       <c r="H6" t="n">
-        <v>1971</v>
+        <v>-5548</v>
       </c>
       <c r="I6" t="n">
-        <v>92</v>
+        <v>793</v>
       </c>
       <c r="J6" t="n">
-        <v>77</v>
+        <v>1104</v>
       </c>
       <c r="K6" t="n">
-        <v>139</v>
+        <v>445</v>
       </c>
       <c r="L6" t="n">
-        <v>2777</v>
+        <v>5732</v>
       </c>
       <c r="M6" t="n">
-        <v>14566</v>
+        <v>24474</v>
       </c>
       <c r="N6" t="n">
-        <v>-78802</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-5.71</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+        <v>-648959</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1324,12 +1459,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1338,47 +1473,39 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1335</v>
+        <v>1900</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6.37</v>
+        <v>1.88</v>
       </c>
       <c r="F7" t="n">
-        <v>13686</v>
+        <v>56489</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-1505</v>
+        <v>-9756</v>
       </c>
       <c r="H7" t="n">
-        <v>-4630</v>
+        <v>-66687</v>
       </c>
       <c r="I7" t="n">
-        <v>793</v>
+        <v>1494</v>
       </c>
       <c r="J7" t="n">
-        <v>1687</v>
+        <v>3947</v>
       </c>
       <c r="K7" t="n">
-        <v>445</v>
+        <v>1823</v>
       </c>
       <c r="L7" t="n">
-        <v>5732</v>
+        <v>22953</v>
       </c>
       <c r="M7" t="n">
-        <v>31108</v>
+        <v>89475</v>
       </c>
       <c r="N7" t="n">
-        <v>-648959</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-3.05</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+        <v>-6482966</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1387,12 +1514,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1401,47 +1528,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1900</v>
+        <v>1420</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>1.88</v>
+        <v>8.81</v>
       </c>
       <c r="F8" t="n">
-        <v>56489</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>-9756</v>
+        <v>4477</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>597</v>
       </c>
       <c r="H8" t="n">
-        <v>-90418</v>
+        <v>-1179</v>
       </c>
       <c r="I8" t="n">
-        <v>1494</v>
+        <v>-62</v>
       </c>
       <c r="J8" t="n">
-        <v>9315</v>
+        <v>-382</v>
       </c>
       <c r="K8" t="n">
-        <v>1823</v>
+        <v>65</v>
       </c>
       <c r="L8" t="n">
-        <v>22953</v>
+        <v>1815</v>
       </c>
       <c r="M8" t="n">
-        <v>111110</v>
+        <v>7673</v>
       </c>
       <c r="N8" t="n">
-        <v>-6482966</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-2.91</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140164</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1450,12 +1569,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1464,47 +1583,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>112</v>
+        <v>1405</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>7.69</v>
+        <v>4.85</v>
       </c>
       <c r="F9" t="n">
-        <v>165823</v>
+        <v>2835</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-13272</v>
+        <v>-110</v>
       </c>
       <c r="H9" t="n">
-        <v>19831</v>
+        <v>-2963</v>
       </c>
       <c r="I9" t="n">
-        <v>-739</v>
+        <v>142</v>
       </c>
       <c r="J9" t="n">
-        <v>7121</v>
+        <v>-560</v>
       </c>
       <c r="K9" t="n">
-        <v>4029</v>
+        <v>172</v>
       </c>
       <c r="L9" t="n">
-        <v>130633</v>
+        <v>3031</v>
       </c>
       <c r="M9" t="n">
-        <v>660143</v>
+        <v>8891</v>
       </c>
       <c r="N9" t="n">
-        <v>-1112633</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106279</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1539,13 +1650,13 @@
         <v>-762</v>
       </c>
       <c r="H10" t="n">
-        <v>-196</v>
+        <v>-208</v>
       </c>
       <c r="I10" t="n">
         <v>658</v>
       </c>
       <c r="J10" t="n">
-        <v>217</v>
+        <v>41</v>
       </c>
       <c r="K10" t="n">
         <v>149</v>
@@ -1554,20 +1665,12 @@
         <v>1828</v>
       </c>
       <c r="M10" t="n">
-        <v>9808</v>
+        <v>7724</v>
       </c>
       <c r="N10" t="n">
         <v>-89500</v>
       </c>
-      <c r="O10" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1576,12 +1679,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1590,47 +1693,39 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3270</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>4.81</v>
+        <v>1985</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>-5.48</v>
       </c>
       <c r="F11" t="n">
-        <v>1497</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>161</v>
+        <v>6795</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-598</v>
       </c>
       <c r="H11" t="n">
-        <v>-578</v>
+        <v>474</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>-56</v>
       </c>
       <c r="J11" t="n">
-        <v>323</v>
+        <v>252</v>
       </c>
       <c r="K11" t="n">
-        <v>33</v>
+        <v>197</v>
       </c>
       <c r="L11" t="n">
-        <v>5978</v>
+        <v>4571</v>
       </c>
       <c r="M11" t="n">
-        <v>29400</v>
+        <v>17431</v>
       </c>
       <c r="N11" t="n">
-        <v>-19738</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-3.17</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+        <v>-19159</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1639,12 +1734,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1653,47 +1748,39 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1985</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>-5.48</v>
+        <v>4775</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>5.52</v>
       </c>
       <c r="F12" t="n">
-        <v>6795</v>
+        <v>297</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-598</v>
+        <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>-115</v>
+        <v>24</v>
       </c>
       <c r="I12" t="n">
-        <v>-56</v>
+        <v>-7</v>
       </c>
       <c r="J12" t="n">
-        <v>838</v>
+        <v>51</v>
       </c>
       <c r="K12" t="n">
-        <v>197</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>4571</v>
+        <v>327</v>
       </c>
       <c r="M12" t="n">
-        <v>21617</v>
+        <v>1262</v>
       </c>
       <c r="N12" t="n">
-        <v>-19159</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-9.85</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8890</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1716,25 +1803,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1365</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>-1.8</v>
+        <v>2315</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>9343</v>
+        <v>2730</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>-1117</v>
       </c>
       <c r="H13" t="n">
-        <v>-166</v>
+        <v>-247</v>
       </c>
       <c r="I13" t="n">
         <v>146</v>
       </c>
       <c r="J13" t="n">
-        <v>788</v>
+        <v>715</v>
       </c>
       <c r="K13" t="n">
         <v>-97</v>
@@ -1743,20 +1830,12 @@
         <v>132</v>
       </c>
       <c r="M13" t="n">
-        <v>-285</v>
+        <v>-75</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1765,12 +1844,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1779,47 +1858,39 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>285</v>
+        <v>449.5</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>8.779999999999999</v>
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>12585</v>
+        <v>3871</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-105</v>
+        <v>-45</v>
       </c>
       <c r="H14" t="n">
-        <v>-11947</v>
+        <v>-1244</v>
       </c>
       <c r="I14" t="n">
-        <v>-1</v>
+        <v>-1639</v>
       </c>
       <c r="J14" t="n">
-        <v>-5091</v>
+        <v>-214</v>
       </c>
       <c r="K14" t="n">
-        <v>265</v>
+        <v>-139</v>
       </c>
       <c r="L14" t="n">
-        <v>542</v>
+        <v>372</v>
       </c>
       <c r="M14" t="n">
-        <v>1692</v>
+        <v>-813</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1828,12 +1899,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台新科</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1842,44 +1913,39 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>137.5</v>
+        <v>974</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>8.27</v>
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>1950</v>
+        <v>1350</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>390</v>
+        <v>343</v>
       </c>
       <c r="H15" t="n">
-        <v>-657</v>
+        <v>4585</v>
+      </c>
+      <c r="I15" t="n">
+        <v>119</v>
       </c>
       <c r="J15" t="n">
-        <v>-5</v>
+        <v>188</v>
       </c>
       <c r="K15" t="n">
-        <v>213</v>
+        <v>43</v>
       </c>
       <c r="L15" t="n">
-        <v>-90</v>
+        <v>16</v>
       </c>
       <c r="M15" t="n">
-        <v>63</v>
+        <v>330</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1888,12 +1954,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1902,613 +1968,41 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>400</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>-4.42</v>
+        <v>1600</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>7565</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>-45</v>
+        <v>904</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>276</v>
       </c>
       <c r="H16" t="n">
-        <v>118</v>
+        <v>-55</v>
       </c>
       <c r="I16" t="n">
-        <v>-1639</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>1546</v>
+        <v>-27</v>
       </c>
       <c r="K16" t="n">
-        <v>-139</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>372</v>
+        <v>-19</v>
       </c>
       <c r="M16" t="n">
-        <v>-1719</v>
+        <v>-79</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3491</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>昇達科</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1380</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="F17" t="n">
-        <v>760</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>-99</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-124</v>
-      </c>
-      <c r="I17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-37</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-19</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-41</v>
-      </c>
-      <c r="M17" t="n">
-        <v>186</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3138</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>耀登</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>-6.65</v>
-      </c>
-      <c r="F18" t="n">
-        <v>12335</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>-768</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1390</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>98</v>
-      </c>
-      <c r="L18" t="n">
-        <v>4212</v>
-      </c>
-      <c r="M18" t="n">
-        <v>24028</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-11466</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-9.470000000000001</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1420</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>8.81</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>4477</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>597</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>-173</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-62</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-439</v>
-      </c>
-      <c r="J19" t="n">
-        <v>65</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1815</v>
-      </c>
-      <c r="L19" t="n">
-        <v>9488</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-140164</v>
-      </c>
-      <c r="N19" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3163</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>波若威</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>718</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1792</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>192</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1055</v>
-      </c>
-      <c r="J20" t="n">
-        <v>14</v>
-      </c>
-      <c r="K20" t="n">
-        <v>-60</v>
-      </c>
-      <c r="L20" t="n">
-        <v>-179</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-570</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>漢唐</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1100</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="n">
-        <v>3894</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>317</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3065</v>
-      </c>
-      <c r="H21" t="n">
-        <v>304</v>
-      </c>
-      <c r="I21" t="n">
-        <v>965</v>
-      </c>
-      <c r="J21" t="n">
-        <v>121</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2151</v>
-      </c>
-      <c r="L21" t="n">
-        <v>10988</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-47552</v>
-      </c>
-      <c r="N21" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>6640</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>均華</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>962</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>826</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>276</v>
-      </c>
-      <c r="G22" t="n">
-        <v>315</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-25</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3</v>
-      </c>
-      <c r="K22" t="n">
-        <v>-19</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-98</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>624</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2040</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>343</v>
-      </c>
-      <c r="G23" t="n">
-        <v>5076</v>
-      </c>
-      <c r="H23" t="n">
-        <v>119</v>
-      </c>
-      <c r="I23" t="n">
-        <v>330</v>
-      </c>
-      <c r="J23" t="n">
-        <v>43</v>
-      </c>
-      <c r="K23" t="n">
-        <v>16</v>
-      </c>
-      <c r="L23" t="n">
-        <v>346</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1405</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2835</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>-110</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-3461</v>
-      </c>
-      <c r="H24" t="n">
-        <v>142</v>
-      </c>
-      <c r="I24" t="n">
-        <v>104</v>
-      </c>
-      <c r="J24" t="n">
-        <v>172</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3031</v>
-      </c>
-      <c r="L24" t="n">
-        <v>11922</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-106279</v>
-      </c>
-      <c r="N24" t="n">
-        <v>16.11</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>3030</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>德律</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>249</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="E25" t="n">
-        <v>10769</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>-467</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2683</v>
-      </c>
-      <c r="H25" t="n">
-        <v>121</v>
-      </c>
-      <c r="I25" t="n">
-        <v>480</v>
-      </c>
-      <c r="J25" t="n">
-        <v>383</v>
-      </c>
-      <c r="K25" t="n">
-        <v>7193</v>
-      </c>
-      <c r="L25" t="n">
-        <v>35567</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-58840</v>
-      </c>
-      <c r="N25" t="n">
-        <v>29.06</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>4775</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="E26" t="n">
-        <v>297</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-172</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-28</v>
-      </c>
-      <c r="J26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K26" t="n">
-        <v>327</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1589</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-8890</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260305.xlsx
+++ b/outputs/monitor_xlsx/20260305.xlsx
@@ -544,10 +544,6 @@
           <t>+2.57%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+3.54%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+2.34%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+1.72%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>-1.07%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>-0.33%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>-1.17%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>+12.29%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>+8.51%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>-514.95億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-584.74億</t>
@@ -811,7 +774,6 @@
           <t>144.67億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>64.83億</t>
@@ -822,8 +784,6 @@
           <t>324.17億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>None%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>-458.02億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>11679口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>16801口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>-31.18億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>2.79億</t>
@@ -1020,10 +966,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1145,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1179,6 +1122,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2004,6 +1948,54 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>276</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1273</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-358</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-574</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-148</v>
+      </c>
+      <c r="J17" t="n">
+        <v>18</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6686</v>
+      </c>
+      <c r="L17" t="n">
+        <v>33425</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-21948</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-3.16</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260305.xlsx
+++ b/outputs/monitor_xlsx/20260305.xlsx
@@ -966,7 +966,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1243,7 +1242,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1251,26 +1250,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>77.40000000000001</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2.38</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>207004</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>-76899</v>
       </c>
       <c r="H4" t="n">
-        <v>-290402</v>
+        <v>-468801</v>
       </c>
       <c r="I4" t="n">
         <v>2300</v>
       </c>
       <c r="J4" t="n">
-        <v>5272</v>
+        <v>10786</v>
       </c>
       <c r="K4" t="n">
         <v>48938</v>
@@ -1279,11 +1278,14 @@
         <v>11144</v>
       </c>
       <c r="M4" t="n">
-        <v>36862</v>
+        <v>48006</v>
       </c>
       <c r="N4" t="n">
         <v>-4279950</v>
       </c>
+      <c r="O4" t="n">
+        <v>2.34</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1306,26 +1308,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>951</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>4.74</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="6" t="n">
         <v>3097</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>-292</v>
       </c>
       <c r="H5" t="n">
-        <v>1457</v>
+        <v>443</v>
       </c>
       <c r="I5" t="n">
         <v>92</v>
       </c>
       <c r="J5" t="n">
-        <v>-259</v>
+        <v>-129</v>
       </c>
       <c r="K5" t="n">
         <v>139</v>
@@ -1334,11 +1336,14 @@
         <v>2777</v>
       </c>
       <c r="M5" t="n">
-        <v>11390</v>
+        <v>14167</v>
       </c>
       <c r="N5" t="n">
         <v>-78802</v>
       </c>
+      <c r="O5" t="n">
+        <v>-2.86</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1361,26 +1366,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1335</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>6.37</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="6" t="n">
         <v>13686</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>-1505</v>
       </c>
       <c r="H6" t="n">
-        <v>-5548</v>
+        <v>-6843</v>
       </c>
       <c r="I6" t="n">
         <v>793</v>
       </c>
       <c r="J6" t="n">
-        <v>1104</v>
+        <v>2059</v>
       </c>
       <c r="K6" t="n">
         <v>445</v>
@@ -1389,11 +1394,14 @@
         <v>5732</v>
       </c>
       <c r="M6" t="n">
-        <v>24474</v>
+        <v>30206</v>
       </c>
       <c r="N6" t="n">
         <v>-648959</v>
       </c>
+      <c r="O6" t="n">
+        <v>4.91</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1416,26 +1424,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1900</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>1.88</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="6" t="n">
         <v>56489</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>-9756</v>
       </c>
       <c r="H7" t="n">
-        <v>-66687</v>
+        <v>-95981</v>
       </c>
       <c r="I7" t="n">
         <v>1494</v>
       </c>
       <c r="J7" t="n">
-        <v>3947</v>
+        <v>8065</v>
       </c>
       <c r="K7" t="n">
         <v>1823</v>
@@ -1444,11 +1452,14 @@
         <v>22953</v>
       </c>
       <c r="M7" t="n">
-        <v>89475</v>
+        <v>112428</v>
       </c>
       <c r="N7" t="n">
         <v>-6482966</v>
       </c>
+      <c r="O7" t="n">
+        <v>2.05</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1471,26 +1482,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1420</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>8.81</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>4477</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>597</v>
       </c>
       <c r="H8" t="n">
-        <v>-1179</v>
+        <v>-173</v>
       </c>
       <c r="I8" t="n">
         <v>-62</v>
       </c>
       <c r="J8" t="n">
-        <v>-382</v>
+        <v>-439</v>
       </c>
       <c r="K8" t="n">
         <v>65</v>
@@ -1499,11 +1510,14 @@
         <v>1815</v>
       </c>
       <c r="M8" t="n">
-        <v>7673</v>
+        <v>9488</v>
       </c>
       <c r="N8" t="n">
         <v>-140164</v>
       </c>
+      <c r="O8" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1526,26 +1540,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>1405</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>4.85</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="6" t="n">
         <v>2835</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>-110</v>
       </c>
       <c r="H9" t="n">
-        <v>-2963</v>
+        <v>-3461</v>
       </c>
       <c r="I9" t="n">
         <v>142</v>
       </c>
       <c r="J9" t="n">
-        <v>-560</v>
+        <v>104</v>
       </c>
       <c r="K9" t="n">
         <v>172</v>
@@ -1554,11 +1568,14 @@
         <v>3031</v>
       </c>
       <c r="M9" t="n">
-        <v>8891</v>
+        <v>11922</v>
       </c>
       <c r="N9" t="n">
         <v>-106279</v>
       </c>
+      <c r="O9" t="n">
+        <v>23.05</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1581,26 +1598,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2365</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>7.99</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="6" t="n">
         <v>3883</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>-762</v>
       </c>
       <c r="H10" t="n">
-        <v>-208</v>
+        <v>-788</v>
       </c>
       <c r="I10" t="n">
         <v>658</v>
       </c>
       <c r="J10" t="n">
-        <v>41</v>
+        <v>801</v>
       </c>
       <c r="K10" t="n">
         <v>149</v>
@@ -1609,11 +1626,14 @@
         <v>1828</v>
       </c>
       <c r="M10" t="n">
-        <v>7724</v>
+        <v>9552</v>
       </c>
       <c r="N10" t="n">
         <v>-89500</v>
       </c>
+      <c r="O10" t="n">
+        <v>13.18</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1636,26 +1656,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>-5.48</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="6" t="n">
         <v>6795</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>-598</v>
       </c>
       <c r="H11" t="n">
-        <v>474</v>
+        <v>-731</v>
       </c>
       <c r="I11" t="n">
         <v>-56</v>
       </c>
       <c r="J11" t="n">
-        <v>252</v>
+        <v>786</v>
       </c>
       <c r="K11" t="n">
         <v>197</v>
@@ -1664,11 +1684,14 @@
         <v>4571</v>
       </c>
       <c r="M11" t="n">
-        <v>17431</v>
+        <v>22002</v>
       </c>
       <c r="N11" t="n">
         <v>-19159</v>
       </c>
+      <c r="O11" t="n">
+        <v>3.91</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1691,26 +1714,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>4775</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>5.52</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="6" t="n">
         <v>297</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>24</v>
+        <v>-172</v>
       </c>
       <c r="I12" t="n">
         <v>-7</v>
       </c>
       <c r="J12" t="n">
-        <v>51</v>
+        <v>-28</v>
       </c>
       <c r="K12" t="n">
         <v>5</v>
@@ -1719,11 +1742,14 @@
         <v>327</v>
       </c>
       <c r="M12" t="n">
-        <v>1262</v>
+        <v>1589</v>
       </c>
       <c r="N12" t="n">
         <v>-8890</v>
       </c>
+      <c r="O12" t="n">
+        <v>4.82</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1746,26 +1772,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="6" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>-1117</v>
       </c>
       <c r="H13" t="n">
-        <v>-247</v>
+        <v>-1232</v>
       </c>
       <c r="I13" t="n">
         <v>146</v>
       </c>
       <c r="J13" t="n">
-        <v>715</v>
+        <v>1004</v>
       </c>
       <c r="K13" t="n">
         <v>-97</v>
@@ -1774,11 +1800,14 @@
         <v>132</v>
       </c>
       <c r="M13" t="n">
-        <v>-75</v>
+        <v>57</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1801,26 +1830,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="6" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>-45</v>
       </c>
       <c r="H14" t="n">
-        <v>-1244</v>
+        <v>-326</v>
       </c>
       <c r="I14" t="n">
         <v>-1639</v>
       </c>
       <c r="J14" t="n">
-        <v>-214</v>
+        <v>-674</v>
       </c>
       <c r="K14" t="n">
         <v>-139</v>
@@ -1829,11 +1858,14 @@
         <v>372</v>
       </c>
       <c r="M14" t="n">
-        <v>-813</v>
+        <v>-441</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1856,26 +1888,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>343</v>
       </c>
       <c r="H15" t="n">
-        <v>4585</v>
+        <v>5076</v>
       </c>
       <c r="I15" t="n">
         <v>119</v>
       </c>
       <c r="J15" t="n">
-        <v>188</v>
+        <v>330</v>
       </c>
       <c r="K15" t="n">
         <v>43</v>
@@ -1884,11 +1916,14 @@
         <v>16</v>
       </c>
       <c r="M15" t="n">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1911,26 +1946,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="7" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>276</v>
       </c>
       <c r="H16" t="n">
-        <v>-55</v>
+        <v>315</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>-27</v>
+        <v>-25</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
@@ -1939,11 +1974,14 @@
         <v>-19</v>
       </c>
       <c r="M16" t="n">
-        <v>-79</v>
+        <v>-98</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1961,41 +1999,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>276</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>3.76</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="6" t="n">
         <v>1273</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="6" t="n">
         <v>-358</v>
       </c>
-      <c r="G17" t="n">
-        <v>-574</v>
-      </c>
       <c r="H17" t="n">
+        <v>-482</v>
+      </c>
+      <c r="I17" t="n">
         <v>-9</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>-148</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>18</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>6686</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>33425</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-21948</v>
       </c>
-      <c r="N17" t="n">
-        <v>-3.16</v>
+      <c r="O17" t="n">
+        <v>8.960000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260305.xlsx
+++ b/outputs/monitor_xlsx/20260305.xlsx
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2041,156 @@
         <v>8.960000000000001</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1775</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8337</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-1556</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-9024</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>512</v>
+      </c>
+      <c r="K18" t="n">
+        <v>500</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5849</v>
+      </c>
+      <c r="M18" t="n">
+        <v>23256</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400923</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>450</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="F19" t="n">
+        <v>18583</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>1513</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-2702</v>
+      </c>
+      <c r="I19" t="n">
+        <v>708</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-452</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1840</v>
+      </c>
+      <c r="L19" t="n">
+        <v>39258</v>
+      </c>
+      <c r="M19" t="n">
+        <v>164587</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-391991</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>461</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4226</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2346</v>
+      </c>
+      <c r="I20" t="n">
+        <v>608</v>
+      </c>
+      <c r="J20" t="n">
+        <v>631</v>
+      </c>
+      <c r="K20" t="n">
+        <v>308</v>
+      </c>
+      <c r="L20" t="n">
+        <v>10048</v>
+      </c>
+      <c r="M20" t="n">
+        <v>44964</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-161246</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
